--- a/data/merged/2026-09-09/MERGED_FR_Mite-Vacuum_2026-09-09.xlsx
+++ b/data/merged/2026-09-09/MERGED_FR_Mite-Vacuum_2026-09-09.xlsx
@@ -4655,13 +4655,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4743,13 +4743,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4837,7 +4837,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4881,7 +4881,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4919,13 +4919,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4942,50 +4942,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId33" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Product 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId34" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5327,7 +5283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR35"/>
+  <dimension ref="A1:BR34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -9818,40 +9774,40 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0DWJQ9GFY</t>
+          <t>B0F6XNKG8M</t>
         </is>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Hocomay</t>
+          <t>Tiazhan</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Hocomay</t>
+          <t>https://www.amazon.fr/stores/Tiazhan/page/E3AC215A-FE9C-439B-85FE-2B790F1088F2?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Hocomay Aspirateur sans fil avec lumière UV-C, aspirateur à main 16 kPa avec écran LED, filtre HEPA, ultrasons, aspirateur de</t>
+          <t>Tiazhan Aspirateur Matelas Anti Acariens, Lumière UV-C et 400 WsÉlimine 99,9% | Air Chaud à 60 °C, Filtre HEPA et Dépoussiér</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0DWJQ9GFY?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F6XNKG8M?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41B77IYi3sL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0DWJQ9GFY</t>
+          <t>B0F6XNKG8M</t>
         </is>
       </c>
       <c r="M21" s="14" t="inlineStr">
@@ -9865,7 +9821,7 @@
         </is>
       </c>
       <c r="O21" s="15">
-        <v>2510320</v>
+        <v>1072003</v>
       </c>
       <c r="P21" s="15"/>
       <c r="Q21" s="16">
@@ -9878,7 +9834,7 @@
       </c>
       <c r="S21" s="18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="T21" s="15"/>
@@ -9890,35 +9846,37 @@
         <v>1</v>
       </c>
       <c r="Z21" s="20">
-        <v>49.99</v>
+        <v>65.99</v>
       </c>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21" s="2"/>
       <c r="AD21" s="19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE21" s="15">
         <v>0</v>
       </c>
       <c r="AF21" s="21">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AG21" s="22">
         <v>0</v>
       </c>
-      <c r="AH21" s="20"/>
+      <c r="AH21" s="20">
+        <v>8.34</v>
+      </c>
       <c r="AI21" s="16">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AJ21"/>
       <c r="AK21" s="13" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AL21" s="19">
-        <v>579</v>
+        <v>316</v>
       </c>
       <c r="AM21" s="13" t="inlineStr">
         <is>
@@ -9928,13 +9886,15 @@
       <c r="AN21" s="13"/>
       <c r="AO21" s="13"/>
       <c r="AP21"/>
-      <c r="AQ21" s="19"/>
+      <c r="AQ21" s="19">
+        <v>8</v>
+      </c>
       <c r="AR21" s="19">
         <v>1</v>
       </c>
       <c r="AS21" s="14" t="inlineStr">
         <is>
-          <t>Luckily Baby</t>
+          <t>NOEL AND RUTH JOHNSTON LTD</t>
         </is>
       </c>
       <c r="AT21" s="13" t="inlineStr">
@@ -9942,11 +9902,19 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU21" s="13"/>
-      <c r="AV21" s="14"/>
+      <c r="AU21" s="13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AV21" s="14" t="inlineStr">
+        <is>
+          <t>NORTHERN IRELAND BT2 7FD GB</t>
+        </is>
+      </c>
       <c r="AW21" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JWI8CSWZ8XWG</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P6U062ILG5ZO</t>
         </is>
       </c>
       <c r="AX21" s="13"/>
@@ -9954,7 +9922,11 @@
       <c r="AZ21" s="13"/>
       <c r="BA21" s="13"/>
       <c r="BB21" s="13"/>
-      <c r="BC21" s="13"/>
+      <c r="BC21" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD21" s="13"/>
       <c r="BE21" s="13"/>
       <c r="BF21" s="13"/>
@@ -9963,25 +9935,45 @@
       <c r="BI21" s="23"/>
       <c r="BJ21" s="23" t="inlineStr">
         <is>
-          <t>2,3 Kilograms</t>
+          <t>2,06 Kilograms</t>
         </is>
       </c>
       <c r="BK21" s="23" t="inlineStr">
         <is>
-          <t>2.30 kg</t>
+          <t>2.06 kg</t>
         </is>
       </c>
       <c r="BL21" s="23" t="inlineStr">
         <is>
-          <t>29L x 27l x 18H centimètres</t>
+          <t>28L x 15l x 68H centimètres</t>
         </is>
       </c>
       <c r="BM21" s="23"/>
-      <c r="BN21" s="23"/>
-      <c r="BO21" s="23"/>
-      <c r="BP21" s="23"/>
-      <c r="BQ21" s="23"/>
-      <c r="BR21" s="13"/>
+      <c r="BN21" s="23" t="inlineStr">
+        <is>
+          <t>2.06 kg</t>
+        </is>
+      </c>
+      <c r="BO21" s="23" t="inlineStr">
+        <is>
+          <t>2.06 kg</t>
+        </is>
+      </c>
+      <c r="BP21" s="23" t="inlineStr">
+        <is>
+          <t>34.4 x 28.5 x 22.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ21" s="23" t="inlineStr">
+        <is>
+          <t>34.40 x 28.50 x 22.20 cm</t>
+        </is>
+      </c>
+      <c r="BR21" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
@@ -9990,40 +9982,40 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Tiazhan</t>
+          <t>Liwankaqi</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Tiazhan/page/E3AC215A-FE9C-439B-85FE-2B790F1088F2?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Tiazhan Aspirateur Matelas Anti Acariens, Lumière UV-C et 400 WsÉlimine 99,9% | Air Chaud à 60 °C, Filtre HEPA et Dépoussiér</t>
+          <t>Liwankaqi Aspirateur anti-acariens pour matelas, avec UV C et ultrasons, aspiration 8 KPa, sans fil, anti-allergène, pour lit</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F6XNKG8M?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F9NJM4V9?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
@@ -10037,11 +10029,13 @@
         </is>
       </c>
       <c r="O22" s="15">
-        <v>1072003</v>
-      </c>
-      <c r="P22" s="15"/>
+        <v>2380853</v>
+      </c>
+      <c r="P22" s="15">
+        <v>-15871</v>
+      </c>
       <c r="Q22" s="16">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R22" s="17" t="inlineStr">
         <is>
@@ -10050,7 +10044,7 @@
       </c>
       <c r="S22" s="18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T22" s="15"/>
@@ -10062,37 +10056,37 @@
         <v>1</v>
       </c>
       <c r="Z22" s="20">
-        <v>65.99</v>
+        <v>48.22</v>
       </c>
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22" s="2"/>
       <c r="AD22" s="19">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE22" s="15">
         <v>0</v>
       </c>
       <c r="AF22" s="21">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" s="22">
         <v>0</v>
       </c>
       <c r="AH22" s="20">
-        <v>8.34</v>
+        <v>8.44</v>
       </c>
       <c r="AI22" s="16">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="AJ22"/>
       <c r="AK22" s="13" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AL22" s="19">
-        <v>316</v>
+        <v>376</v>
       </c>
       <c r="AM22" s="13" t="inlineStr">
         <is>
@@ -10110,7 +10104,7 @@
       </c>
       <c r="AS22" s="14" t="inlineStr">
         <is>
-          <t>NOEL AND RUTH JOHNSTON LTD</t>
+          <t>liwantech</t>
         </is>
       </c>
       <c r="AT22" s="13" t="inlineStr">
@@ -10120,17 +10114,17 @@
       </c>
       <c r="AU22" s="13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV22" s="14" t="inlineStr">
         <is>
-          <t>NORTHERN IRELAND BT2 7FD GB</t>
+          <t>深圳市 南山区 广东 518000 CN</t>
         </is>
       </c>
       <c r="AW22" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P6U062ILG5ZO</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
         </is>
       </c>
       <c r="AX22" s="13"/>
@@ -10143,7 +10137,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD22" s="13"/>
+      <c r="BD22" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE22" s="13"/>
       <c r="BF22" s="13"/>
       <c r="BG22" s="13"/>
@@ -10151,38 +10149,42 @@
       <c r="BI22" s="23"/>
       <c r="BJ22" s="23" t="inlineStr">
         <is>
-          <t>2,06 Kilograms</t>
+          <t>2.24 kg</t>
         </is>
       </c>
       <c r="BK22" s="23" t="inlineStr">
         <is>
-          <t>2.06 kg</t>
+          <t>2.24 kg</t>
         </is>
       </c>
       <c r="BL22" s="23" t="inlineStr">
         <is>
-          <t>28L x 15l x 68H centimètres</t>
-        </is>
-      </c>
-      <c r="BM22" s="23"/>
+          <t>29.4 x 2.7 x 18.5 cm</t>
+        </is>
+      </c>
+      <c r="BM22" s="23" t="inlineStr">
+        <is>
+          <t>29.40 x 2.70 x 18.50 cm</t>
+        </is>
+      </c>
       <c r="BN22" s="23" t="inlineStr">
         <is>
-          <t>2.06 kg</t>
+          <t>2.24 kg</t>
         </is>
       </c>
       <c r="BO22" s="23" t="inlineStr">
         <is>
-          <t>2.06 kg</t>
+          <t>2.24 kg</t>
         </is>
       </c>
       <c r="BP22" s="23" t="inlineStr">
         <is>
-          <t>34.4 x 28.5 x 22.2 cm</t>
+          <t>34 x 31 x 23 cm</t>
         </is>
       </c>
       <c r="BQ22" s="23" t="inlineStr">
         <is>
-          <t>34.40 x 28.50 x 22.20 cm</t>
+          <t>34.00 x 31.00 x 23.00 cm</t>
         </is>
       </c>
       <c r="BR22" s="13" t="inlineStr">
@@ -10198,40 +10200,40 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
+          <t>https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi Aspirateur anti-acariens pour matelas, avec UV C et ultrasons, aspiration 8 KPa, sans fil, anti-allergène, pour lit</t>
+          <t>JIGOO T600 Aspirateur anti-acariens/Floral Delight (huile essentielle végétale)</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F9NJM4V9?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FDWVV95V?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="M23" s="14" t="inlineStr">
@@ -10245,13 +10247,11 @@
         </is>
       </c>
       <c r="O23" s="15">
-        <v>2380853</v>
-      </c>
-      <c r="P23" s="15">
-        <v>-15871</v>
-      </c>
+        <v>1497681</v>
+      </c>
+      <c r="P23" s="15"/>
       <c r="Q23" s="16">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R23" s="17" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="S23" s="18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T23" s="15"/>
@@ -10272,37 +10272,37 @@
         <v>1</v>
       </c>
       <c r="Z23" s="20">
-        <v>48.22</v>
+        <v>19</v>
       </c>
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="19">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE23" s="15">
         <v>0</v>
       </c>
       <c r="AF23" s="21">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
       </c>
       <c r="AH23" s="20">
-        <v>8.44</v>
+        <v>2.4</v>
       </c>
       <c r="AI23" s="16">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="AJ23"/>
       <c r="AK23" s="13" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AL23" s="19">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="AM23" s="13" t="inlineStr">
         <is>
@@ -10312,15 +10312,13 @@
       <c r="AN23" s="13"/>
       <c r="AO23" s="13"/>
       <c r="AP23"/>
-      <c r="AQ23" s="19">
-        <v>8</v>
-      </c>
+      <c r="AQ23" s="19"/>
       <c r="AR23" s="19">
         <v>1</v>
       </c>
       <c r="AS23" s="14" t="inlineStr">
         <is>
-          <t>liwantech</t>
+          <t>tengjidainzi</t>
         </is>
       </c>
       <c r="AT23" s="13" t="inlineStr">
@@ -10335,12 +10333,12 @@
       </c>
       <c r="AV23" s="14" t="inlineStr">
         <is>
-          <t>深圳市 南山区 广东 518000 CN</t>
+          <t>深圳市 广东 518033 CN</t>
         </is>
       </c>
       <c r="AW23" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1LBASE3VLPMEX</t>
         </is>
       </c>
       <c r="AX23" s="13"/>
@@ -10348,16 +10346,8 @@
       <c r="AZ23" s="13"/>
       <c r="BA23" s="13"/>
       <c r="BB23" s="13"/>
-      <c r="BC23" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD23" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC23" s="13"/>
+      <c r="BD23" s="13"/>
       <c r="BE23" s="13"/>
       <c r="BF23" s="13"/>
       <c r="BG23" s="13"/>
@@ -10365,47 +10355,43 @@
       <c r="BI23" s="23"/>
       <c r="BJ23" s="23" t="inlineStr">
         <is>
-          <t>2.24 kg</t>
+          <t>50 g</t>
         </is>
       </c>
       <c r="BK23" s="23" t="inlineStr">
         <is>
-          <t>2.24 kg</t>
+          <t>50.00 g</t>
         </is>
       </c>
       <c r="BL23" s="23" t="inlineStr">
         <is>
-          <t>29.4 x 2.7 x 18.5 cm</t>
-        </is>
-      </c>
-      <c r="BM23" s="23" t="inlineStr">
-        <is>
-          <t>29.40 x 2.70 x 18.50 cm</t>
-        </is>
-      </c>
+          <t>6L x 1,3l x 8H centimètres</t>
+        </is>
+      </c>
+      <c r="BM23" s="23"/>
       <c r="BN23" s="23" t="inlineStr">
         <is>
-          <t>2.24 kg</t>
+          <t>50 g</t>
         </is>
       </c>
       <c r="BO23" s="23" t="inlineStr">
         <is>
-          <t>2.24 kg</t>
+          <t>50.00 g</t>
         </is>
       </c>
       <c r="BP23" s="23" t="inlineStr">
         <is>
-          <t>34 x 31 x 23 cm</t>
+          <t>10 x 6 x 1.5 cm</t>
         </is>
       </c>
       <c r="BQ23" s="23" t="inlineStr">
         <is>
-          <t>34.00 x 31.00 x 23.00 cm</t>
+          <t>10.00 x 6.00 x 1.50 cm</t>
         </is>
       </c>
       <c r="BR23" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型信封</t>
         </is>
       </c>
     </row>
@@ -10416,40 +10402,40 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FN3V6RFQ</t>
         </is>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>JIGOO</t>
+          <t>Minthouz</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/Minthouz/b/ref=bl_dp_s_web_92236826031?ie=UTF8&amp;node=92236826031&amp;field-lbr_brands_browse-bin=Minthouz</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 Aspirateur anti-acariens/Floral Delight (huile essentielle végétale)</t>
+          <t>Minthouz Aspirateur Anti-acariens</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FDWVV95V?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FN3V6RFQ</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
@@ -10463,7 +10449,7 @@
         </is>
       </c>
       <c r="O24" s="15">
-        <v>1497681</v>
+        <v>1178938</v>
       </c>
       <c r="P24" s="15"/>
       <c r="Q24" s="16">
@@ -10476,7 +10462,7 @@
       </c>
       <c r="S24" s="18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T24" s="15"/>
@@ -10488,37 +10474,37 @@
         <v>1</v>
       </c>
       <c r="Z24" s="20">
-        <v>19</v>
+        <v>96.44</v>
       </c>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="19">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AE24" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" s="21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG24" s="22">
         <v>0</v>
       </c>
       <c r="AH24" s="20">
-        <v>2.4</v>
+        <v>8.11</v>
       </c>
       <c r="AI24" s="16">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="AJ24"/>
       <c r="AK24" s="13" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AL24" s="19">
-        <v>393</v>
+        <v>136</v>
       </c>
       <c r="AM24" s="13" t="inlineStr">
         <is>
@@ -10528,13 +10514,15 @@
       <c r="AN24" s="13"/>
       <c r="AO24" s="13"/>
       <c r="AP24"/>
-      <c r="AQ24" s="19"/>
+      <c r="AQ24" s="19">
+        <v>5</v>
+      </c>
       <c r="AR24" s="19">
         <v>1</v>
       </c>
       <c r="AS24" s="14" t="inlineStr">
         <is>
-          <t>tengjidainzi</t>
+          <t>Minthouz EUDirect</t>
         </is>
       </c>
       <c r="AT24" s="13" t="inlineStr">
@@ -10549,12 +10537,12 @@
       </c>
       <c r="AV24" s="14" t="inlineStr">
         <is>
-          <t>深圳市 广东 518033 CN</t>
+          <t>guangmingqu Guangdong 518100 CN</t>
         </is>
       </c>
       <c r="AW24" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1LBASE3VLPMEX</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A33KFCZH4G272M</t>
         </is>
       </c>
       <c r="AX24" s="13"/>
@@ -10571,43 +10559,43 @@
       <c r="BI24" s="23"/>
       <c r="BJ24" s="23" t="inlineStr">
         <is>
-          <t>50 g</t>
+          <t>3,6 Kilograms</t>
         </is>
       </c>
       <c r="BK24" s="23" t="inlineStr">
         <is>
-          <t>50.00 g</t>
+          <t>3.60 kg</t>
         </is>
       </c>
       <c r="BL24" s="23" t="inlineStr">
         <is>
-          <t>6L x 1,3l x 8H centimètres</t>
+          <t>31,2L x 31,2l x 23,8H centimètres</t>
         </is>
       </c>
       <c r="BM24" s="23"/>
       <c r="BN24" s="23" t="inlineStr">
         <is>
-          <t>50 g</t>
+          <t>3.6 kg</t>
         </is>
       </c>
       <c r="BO24" s="23" t="inlineStr">
         <is>
-          <t>50.00 g</t>
+          <t>3.60 kg</t>
         </is>
       </c>
       <c r="BP24" s="23" t="inlineStr">
         <is>
-          <t>10 x 6 x 1.5 cm</t>
+          <t>31 x 31 x 23.7 cm</t>
         </is>
       </c>
       <c r="BQ24" s="23" t="inlineStr">
         <is>
-          <t>10.00 x 6.00 x 1.50 cm</t>
+          <t>31.00 x 31.00 x 23.70 cm</t>
         </is>
       </c>
       <c r="BR24" s="13" t="inlineStr">
         <is>
-          <t>轻型信封</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -10618,40 +10606,40 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0FN3V6RFQ</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Minthouz</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/Minthouz/b/ref=bl_dp_s_web_92236826031?ie=UTF8&amp;node=92236826031&amp;field-lbr_brands_browse-bin=Minthouz</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Minthouz Aspirateur Anti-acariens</t>
+          <t>Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimine 99,99%</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FYM1D13D?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0FN3V6RFQ</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="M25" s="14" t="inlineStr">
@@ -10665,11 +10653,13 @@
         </is>
       </c>
       <c r="O25" s="15">
-        <v>1178938</v>
-      </c>
-      <c r="P25" s="15"/>
+        <v>2233981</v>
+      </c>
+      <c r="P25" s="15">
+        <v>-17555</v>
+      </c>
       <c r="Q25" s="16">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R25" s="17" t="inlineStr">
         <is>
@@ -10678,7 +10668,7 @@
       </c>
       <c r="S25" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T25" s="15"/>
@@ -10690,37 +10680,37 @@
         <v>1</v>
       </c>
       <c r="Z25" s="20">
-        <v>96.44</v>
+        <v>28.99</v>
       </c>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="19">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="AE25" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF25" s="21">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
       </c>
       <c r="AH25" s="20">
-        <v>8.11</v>
+        <v>5.98</v>
       </c>
       <c r="AI25" s="16">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="AJ25"/>
       <c r="AK25" s="13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL25" s="19">
-        <v>136</v>
+        <v>277</v>
       </c>
       <c r="AM25" s="13" t="inlineStr">
         <is>
@@ -10731,14 +10721,14 @@
       <c r="AO25" s="13"/>
       <c r="AP25"/>
       <c r="AQ25" s="19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AR25" s="19">
         <v>1</v>
       </c>
       <c r="AS25" s="14" t="inlineStr">
         <is>
-          <t>Minthouz EUDirect</t>
+          <t>Renyu</t>
         </is>
       </c>
       <c r="AT25" s="13" t="inlineStr">
@@ -10753,12 +10743,12 @@
       </c>
       <c r="AV25" s="14" t="inlineStr">
         <is>
-          <t>guangmingqu Guangdong 518100 CN</t>
+          <t>dong hu xin ji shu hubei 430223 CN</t>
         </is>
       </c>
       <c r="AW25" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A33KFCZH4G272M</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
         </is>
       </c>
       <c r="AX25" s="13"/>
@@ -10766,7 +10756,11 @@
       <c r="AZ25" s="13"/>
       <c r="BA25" s="13"/>
       <c r="BB25" s="13"/>
-      <c r="BC25" s="13"/>
+      <c r="BC25" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD25" s="13"/>
       <c r="BE25" s="13"/>
       <c r="BF25" s="13"/>
@@ -10775,43 +10769,43 @@
       <c r="BI25" s="23"/>
       <c r="BJ25" s="23" t="inlineStr">
         <is>
-          <t>3,6 Kilograms</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="BK25" s="23" t="inlineStr">
         <is>
-          <t>3.60 kg</t>
+          <t>400.00 g</t>
         </is>
       </c>
       <c r="BL25" s="23" t="inlineStr">
         <is>
-          <t>31,2L x 31,2l x 23,8H centimètres</t>
+          <t>6L x 4l x 8H centimètres</t>
         </is>
       </c>
       <c r="BM25" s="23"/>
       <c r="BN25" s="23" t="inlineStr">
         <is>
-          <t>3.6 kg</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="BO25" s="23" t="inlineStr">
         <is>
-          <t>3.60 kg</t>
+          <t>400.00 g</t>
         </is>
       </c>
       <c r="BP25" s="23" t="inlineStr">
         <is>
-          <t>31 x 31 x 23.7 cm</t>
+          <t>23.8 x 11.7 x 10.2 cm</t>
         </is>
       </c>
       <c r="BQ25" s="23" t="inlineStr">
         <is>
-          <t>31.00 x 31.00 x 23.70 cm</t>
+          <t>23.80 x 11.70 x 10.20 cm</t>
         </is>
       </c>
       <c r="BR25" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -10822,40 +10816,40 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0GF7CNTYL</t>
         </is>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>Liwankaqi</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimine 99,99%</t>
+          <t>Aspirateur de Matelas UV-C Ultrasonique pour Lit et CanapésAspirateur sans fil pour housses de couette, matelas, canapés en</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FYM1D13D?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GF7CNTYL?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0GF7CNTYL</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
@@ -10869,13 +10863,13 @@
         </is>
       </c>
       <c r="O26" s="15">
-        <v>2233981</v>
+        <v>1572373</v>
       </c>
       <c r="P26" s="15">
-        <v>-17555</v>
+        <v>-325725</v>
       </c>
       <c r="Q26" s="16">
-        <v>-0.01</v>
+        <v>-0.26</v>
       </c>
       <c r="R26" s="17" t="inlineStr">
         <is>
@@ -10884,7 +10878,7 @@
       </c>
       <c r="S26" s="18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T26" s="15"/>
@@ -10896,60 +10890,52 @@
         <v>1</v>
       </c>
       <c r="Z26" s="20">
-        <v>28.99</v>
+        <v>39.99</v>
       </c>
       <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26" s="2"/>
-      <c r="AD26" s="19">
-        <v>4</v>
-      </c>
-      <c r="AE26" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="21">
-        <v>3</v>
-      </c>
+      <c r="AD26" s="19"/>
+      <c r="AE26" s="15"/>
+      <c r="AF26" s="21"/>
       <c r="AG26" s="22">
         <v>0</v>
       </c>
       <c r="AH26" s="20">
-        <v>5.98</v>
+        <v>7.29</v>
       </c>
       <c r="AI26" s="16">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="AJ26"/>
       <c r="AK26" s="13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AL26" s="19">
-        <v>277</v>
+        <v>149</v>
       </c>
       <c r="AM26" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN26" s="13"/>
       <c r="AO26" s="13"/>
       <c r="AP26"/>
-      <c r="AQ26" s="19">
-        <v>8</v>
-      </c>
+      <c r="AQ26" s="19"/>
       <c r="AR26" s="19">
         <v>1</v>
       </c>
       <c r="AS26" s="14" t="inlineStr">
         <is>
-          <t>Renyu</t>
+          <t>liwantech</t>
         </is>
       </c>
       <c r="AT26" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU26" s="13" t="inlineStr">
@@ -10959,12 +10945,12 @@
       </c>
       <c r="AV26" s="14" t="inlineStr">
         <is>
-          <t>dong hu xin ji shu hubei 430223 CN</t>
+          <t>深圳市 南山区 广东 518000 CN</t>
         </is>
       </c>
       <c r="AW26" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
         </is>
       </c>
       <c r="AX26" s="13"/>
@@ -10972,11 +10958,7 @@
       <c r="AZ26" s="13"/>
       <c r="BA26" s="13"/>
       <c r="BB26" s="13"/>
-      <c r="BC26" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC26" s="13"/>
       <c r="BD26" s="13"/>
       <c r="BE26" s="13"/>
       <c r="BF26" s="13"/>
@@ -10985,43 +10967,47 @@
       <c r="BI26" s="23"/>
       <c r="BJ26" s="23" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>1.3 kg</t>
         </is>
       </c>
       <c r="BK26" s="23" t="inlineStr">
         <is>
-          <t>400.00 g</t>
+          <t>1.30 kg</t>
         </is>
       </c>
       <c r="BL26" s="23" t="inlineStr">
         <is>
-          <t>6L x 4l x 8H centimètres</t>
-        </is>
-      </c>
-      <c r="BM26" s="23"/>
+          <t>28 x 27 x 11 cm</t>
+        </is>
+      </c>
+      <c r="BM26" s="23" t="inlineStr">
+        <is>
+          <t>28.00 x 27.00 x 11.00 cm</t>
+        </is>
+      </c>
       <c r="BN26" s="23" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>1.3 kg</t>
         </is>
       </c>
       <c r="BO26" s="23" t="inlineStr">
         <is>
-          <t>400.00 g</t>
+          <t>1.30 kg</t>
         </is>
       </c>
       <c r="BP26" s="23" t="inlineStr">
         <is>
-          <t>23.8 x 11.7 x 10.2 cm</t>
+          <t>28 x 27 x 17 cm</t>
         </is>
       </c>
       <c r="BQ26" s="23" t="inlineStr">
         <is>
-          <t>23.80 x 11.70 x 10.20 cm</t>
+          <t>28.00 x 27.00 x 17.00 cm</t>
         </is>
       </c>
       <c r="BR26" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -11032,40 +11018,40 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
+          <t>B0GGBLWNRZ</t>
         </is>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi</t>
+          <t>Ubric</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Ubric</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur de Matelas UV-C Ultrasonique pour Lit et CanapésAspirateur sans fil pour housses de couette, matelas, canapés en</t>
+          <t>Ubric Aspirateur sans fil anti-acariens, avec filtre HEPA, aspirateur de matelas sans fil pour matelas, canapé, coussin, tapi</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GF7CNTYL?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/312AapwBZZL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
+          <t>B0GGBLWNRZ</t>
         </is>
       </c>
       <c r="M27" s="14" t="inlineStr">
@@ -11073,30 +11059,12 @@
           <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
         </is>
       </c>
-      <c r="N27" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O27" s="15">
-        <v>1572373</v>
-      </c>
-      <c r="P27" s="15">
-        <v>-325725</v>
-      </c>
-      <c r="Q27" s="16">
-        <v>-0.26</v>
-      </c>
-      <c r="R27" s="17" t="inlineStr">
-        <is>
-          <t>Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="S27" s="18" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="N27" s="14"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="18"/>
       <c r="T27" s="15"/>
       <c r="U27" s="16"/>
       <c r="V27" s="15"/>
@@ -11106,31 +11074,35 @@
         <v>1</v>
       </c>
       <c r="Z27" s="20">
-        <v>39.99</v>
+        <v>20.99</v>
       </c>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27" s="2"/>
-      <c r="AD27" s="19"/>
-      <c r="AE27" s="15"/>
-      <c r="AF27" s="21"/>
+      <c r="AD27" s="19">
+        <v>2</v>
+      </c>
+      <c r="AE27" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="21">
+        <v>3</v>
+      </c>
       <c r="AG27" s="22">
         <v>0</v>
       </c>
-      <c r="AH27" s="20">
-        <v>7.29</v>
-      </c>
+      <c r="AH27" s="20"/>
       <c r="AI27" s="16">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AJ27"/>
       <c r="AK27" s="13" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="AL27" s="19">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="AM27" s="13" t="inlineStr">
         <is>
@@ -11146,7 +11118,7 @@
       </c>
       <c r="AS27" s="14" t="inlineStr">
         <is>
-          <t>liwantech</t>
+          <t>Ubric</t>
         </is>
       </c>
       <c r="AT27" s="13" t="inlineStr">
@@ -11154,19 +11126,11 @@
           <t>FBA</t>
         </is>
       </c>
-      <c r="AU27" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV27" s="14" t="inlineStr">
-        <is>
-          <t>深圳市 南山区 广东 518000 CN</t>
-        </is>
-      </c>
+      <c r="AU27" s="13"/>
+      <c r="AV27" s="14"/>
       <c r="AW27" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2T66IN8FDYP42</t>
         </is>
       </c>
       <c r="AX27" s="13"/>
@@ -11183,49 +11147,21 @@
       <c r="BI27" s="23"/>
       <c r="BJ27" s="23" t="inlineStr">
         <is>
-          <t>1.3 kg</t>
+          <t>410 g</t>
         </is>
       </c>
       <c r="BK27" s="23" t="inlineStr">
         <is>
-          <t>1.30 kg</t>
-        </is>
-      </c>
-      <c r="BL27" s="23" t="inlineStr">
-        <is>
-          <t>28 x 27 x 11 cm</t>
-        </is>
-      </c>
-      <c r="BM27" s="23" t="inlineStr">
-        <is>
-          <t>28.00 x 27.00 x 11.00 cm</t>
-        </is>
-      </c>
-      <c r="BN27" s="23" t="inlineStr">
-        <is>
-          <t>1.3 kg</t>
-        </is>
-      </c>
-      <c r="BO27" s="23" t="inlineStr">
-        <is>
-          <t>1.30 kg</t>
-        </is>
-      </c>
-      <c r="BP27" s="23" t="inlineStr">
-        <is>
-          <t>28 x 27 x 17 cm</t>
-        </is>
-      </c>
-      <c r="BQ27" s="23" t="inlineStr">
-        <is>
-          <t>28.00 x 27.00 x 17.00 cm</t>
-        </is>
-      </c>
-      <c r="BR27" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+          <t>410.00 g</t>
+        </is>
+      </c>
+      <c r="BL27" s="23"/>
+      <c r="BM27" s="23"/>
+      <c r="BN27" s="23"/>
+      <c r="BO27" s="23"/>
+      <c r="BP27" s="23"/>
+      <c r="BQ27" s="23"/>
+      <c r="BR27" s="13"/>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13">
@@ -11234,40 +11170,40 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0GGBLWNRZ</t>
+          <t>B0GMPVWCZM</t>
         </is>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>Ubric</t>
+          <t>Elecbee</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Ubric</t>
+          <t>https://www.amazon.fr/Elecbee/b/ref=bl_dp_s_web_52327091031?ie=UTF8&amp;node=52327091031&amp;field-lbr_brands_browse-bin=Elecbee</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Ubric Aspirateur sans fil anti-acariens, avec filtre HEPA, aspirateur de matelas sans fil pour matelas, canapé, coussin, tapi</t>
+          <t>Elecbee Aspirateur anti-acariens sans fil pour matelas, avec lumière UV, affichage LED, technologie ultrasonique, aspirateur</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GMPVWCZM?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/312AapwBZZL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/41tqM0+3BpL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0GGBLWNRZ</t>
+          <t>B0GMPVWCZM</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
@@ -11290,19 +11226,19 @@
         <v>1</v>
       </c>
       <c r="Z28" s="20">
-        <v>20.99</v>
+        <v>75.99</v>
       </c>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="19">
+        <v>1</v>
+      </c>
+      <c r="AE28" s="15">
         <v>2</v>
       </c>
-      <c r="AE28" s="15">
-        <v>0</v>
-      </c>
       <c r="AF28" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -11314,11 +11250,11 @@
       <c r="AJ28"/>
       <c r="AK28" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AL28" s="19">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="AM28" s="13" t="inlineStr">
         <is>
@@ -11334,7 +11270,7 @@
       </c>
       <c r="AS28" s="14" t="inlineStr">
         <is>
-          <t>Ubric</t>
+          <t>WUHAN RENHOTEC TECHNOLOGY LTD</t>
         </is>
       </c>
       <c r="AT28" s="13" t="inlineStr">
@@ -11346,7 +11282,7 @@
       <c r="AV28" s="14"/>
       <c r="AW28" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2T66IN8FDYP42</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O</t>
         </is>
       </c>
       <c r="AX28" s="13"/>
@@ -11354,7 +11290,11 @@
       <c r="AZ28" s="13"/>
       <c r="BA28" s="13"/>
       <c r="BB28" s="13"/>
-      <c r="BC28" s="13"/>
+      <c r="BC28" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD28" s="13"/>
       <c r="BE28" s="13"/>
       <c r="BF28" s="13"/>
@@ -11363,15 +11303,19 @@
       <c r="BI28" s="23"/>
       <c r="BJ28" s="23" t="inlineStr">
         <is>
-          <t>410 g</t>
+          <t>2 Kilograms</t>
         </is>
       </c>
       <c r="BK28" s="23" t="inlineStr">
         <is>
-          <t>410.00 g</t>
-        </is>
-      </c>
-      <c r="BL28" s="23"/>
+          <t>2.00 kg</t>
+        </is>
+      </c>
+      <c r="BL28" s="23" t="inlineStr">
+        <is>
+          <t>20L x 30l x 20H centimètres</t>
+        </is>
+      </c>
       <c r="BM28" s="23"/>
       <c r="BN28" s="23"/>
       <c r="BO28" s="23"/>
@@ -11386,40 +11330,40 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0GMPVWCZM</t>
+          <t>B0GT17NK5X</t>
         </is>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Elecbee</t>
+          <t>XINYUDAILY</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/Elecbee/b/ref=bl_dp_s_web_52327091031?ie=UTF8&amp;node=52327091031&amp;field-lbr_brands_browse-bin=Elecbee</t>
+          <t>https://www.amazon.fr/XINYUDAILY/b/ref=bl_dp_s_web_85011884031?ie=UTF8&amp;node=85011884031&amp;field-lbr_brands_browse-bin=XINYUDAILY</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Elecbee Aspirateur anti-acariens sans fil pour matelas, avec lumière UV, affichage LED, technologie ultrasonique, aspirateur</t>
+          <t>Aspirateur anti-acariens sans fil pour matelas, avec lumière UV de 253,7 nm, ultrasons et tapotements de rouleau de brosse, a</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GMPVWCZM?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GT17NK5X?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/41tqM0+3BpL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0GMPVWCZM</t>
+          <t>B0GT17NK5X</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
@@ -11427,12 +11371,28 @@
           <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
         </is>
       </c>
-      <c r="N29" s="14"/>
-      <c r="O29" s="15"/>
+      <c r="N29" s="14" t="inlineStr">
+        <is>
+          <t>Voir les 100 premiers en Cuisine et Maison</t>
+        </is>
+      </c>
+      <c r="O29" s="15">
+        <v>392069</v>
+      </c>
       <c r="P29" s="15"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="18"/>
+      <c r="Q29" s="16">
+        <v>0</v>
+      </c>
+      <c r="R29" s="17" t="inlineStr">
+        <is>
+          <t>Aspirateurs pour futons</t>
+        </is>
+      </c>
+      <c r="S29" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="T29" s="15"/>
       <c r="U29" s="16"/>
       <c r="V29" s="15"/>
@@ -11442,7 +11402,7 @@
         <v>1</v>
       </c>
       <c r="Z29" s="20">
-        <v>75.99</v>
+        <v>69.99</v>
       </c>
       <c r="AA29"/>
       <c r="AB29"/>
@@ -11451,7 +11411,7 @@
         <v>1</v>
       </c>
       <c r="AE29" s="15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF29" s="21">
         <v>5</v>
@@ -11459,18 +11419,20 @@
       <c r="AG29" s="22">
         <v>0</v>
       </c>
-      <c r="AH29" s="20"/>
+      <c r="AH29" s="20">
+        <v>8.03</v>
+      </c>
       <c r="AI29" s="16">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AJ29"/>
       <c r="AK29" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AL29" s="19">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="AM29" s="13" t="inlineStr">
         <is>
@@ -11486,7 +11448,7 @@
       </c>
       <c r="AS29" s="14" t="inlineStr">
         <is>
-          <t>WUHAN RENHOTEC TECHNOLOGY LTD</t>
+          <t>XINYU-EU</t>
         </is>
       </c>
       <c r="AT29" s="13" t="inlineStr">
@@ -11494,11 +11456,19 @@
           <t>FBA</t>
         </is>
       </c>
-      <c r="AU29" s="13"/>
-      <c r="AV29" s="14"/>
+      <c r="AU29" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV29" s="14" t="inlineStr">
+        <is>
+          <t>营口市 鲅鱼圈区 辽宁省 115007 CN</t>
+        </is>
+      </c>
       <c r="AW29" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY</t>
         </is>
       </c>
       <c r="AX29" s="13"/>
@@ -11506,38 +11476,54 @@
       <c r="AZ29" s="13"/>
       <c r="BA29" s="13"/>
       <c r="BB29" s="13"/>
-      <c r="BC29" s="13" t="inlineStr">
+      <c r="BC29" s="13"/>
+      <c r="BD29" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD29" s="13"/>
       <c r="BE29" s="13"/>
       <c r="BF29" s="13"/>
       <c r="BG29" s="13"/>
       <c r="BH29" s="14"/>
       <c r="BI29" s="23"/>
-      <c r="BJ29" s="23" t="inlineStr">
-        <is>
-          <t>2 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK29" s="23" t="inlineStr">
-        <is>
-          <t>2.00 kg</t>
-        </is>
-      </c>
+      <c r="BJ29" s="23"/>
+      <c r="BK29" s="23"/>
       <c r="BL29" s="23" t="inlineStr">
         <is>
-          <t>20L x 30l x 20H centimètres</t>
-        </is>
-      </c>
-      <c r="BM29" s="23"/>
-      <c r="BN29" s="23"/>
-      <c r="BO29" s="23"/>
-      <c r="BP29" s="23"/>
-      <c r="BQ29" s="23"/>
-      <c r="BR29" s="13"/>
+          <t>32 x 29 x 21 cm</t>
+        </is>
+      </c>
+      <c r="BM29" s="23" t="inlineStr">
+        <is>
+          <t>32.00 x 29.00 x 21.00 cm</t>
+        </is>
+      </c>
+      <c r="BN29" s="23" t="inlineStr">
+        <is>
+          <t>2.2 kg</t>
+        </is>
+      </c>
+      <c r="BO29" s="23" t="inlineStr">
+        <is>
+          <t>2.20 kg</t>
+        </is>
+      </c>
+      <c r="BP29" s="23" t="inlineStr">
+        <is>
+          <t>32 x 29 x 21 cm</t>
+        </is>
+      </c>
+      <c r="BQ29" s="23" t="inlineStr">
+        <is>
+          <t>32.00 x 29.00 x 21.00 cm</t>
+        </is>
+      </c>
+      <c r="BR29" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
@@ -11546,40 +11532,40 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0GT17NK5X</t>
+          <t>B0GWH1FGJB</t>
         </is>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>XINYUDAILY</t>
+          <t>Timisea</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/XINYUDAILY/b/ref=bl_dp_s_web_85011884031?ie=UTF8&amp;node=85011884031&amp;field-lbr_brands_browse-bin=XINYUDAILY</t>
+          <t>https://www.amazon.fr/Timisea/b/ref=bl_dp_s_web_93230377031?ie=UTF8&amp;node=93230377031&amp;field-lbr_brands_browse-bin=Timisea</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur anti-acariens sans fil pour matelas, avec lumière UV de 253,7 nm, ultrasons et tapotements de rouleau de brosse, a</t>
+          <t>Aspirateur anti-acariens 2 en 1 pour matelas, stérilisation à lumière bleue et haute fréquence, puissant nettoyeur de matelas</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GT17NK5X?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GWH1FGJB?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0GT17NK5X</t>
+          <t>B0GWH1FGJB</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
@@ -11593,7 +11579,7 @@
         </is>
       </c>
       <c r="O30" s="15">
-        <v>392069</v>
+        <v>335413</v>
       </c>
       <c r="P30" s="15"/>
       <c r="Q30" s="16">
@@ -11606,7 +11592,7 @@
       </c>
       <c r="S30" s="18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T30" s="15"/>
@@ -11618,37 +11604,31 @@
         <v>1</v>
       </c>
       <c r="Z30" s="20">
-        <v>69.99</v>
+        <v>35.99</v>
       </c>
       <c r="AA30"/>
       <c r="AB30"/>
       <c r="AC30" s="2"/>
-      <c r="AD30" s="19">
-        <v>1</v>
-      </c>
-      <c r="AE30" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF30" s="21">
-        <v>5</v>
-      </c>
+      <c r="AD30" s="19"/>
+      <c r="AE30" s="15"/>
+      <c r="AF30" s="21"/>
       <c r="AG30" s="22">
         <v>0</v>
       </c>
       <c r="AH30" s="20">
-        <v>8.03</v>
+        <v>6.06</v>
       </c>
       <c r="AI30" s="16">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="AJ30"/>
       <c r="AK30" s="13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AL30" s="19">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="AM30" s="13" t="inlineStr">
         <is>
@@ -11664,7 +11644,7 @@
       </c>
       <c r="AS30" s="14" t="inlineStr">
         <is>
-          <t>XINYU-EU</t>
+          <t>Alloplectus</t>
         </is>
       </c>
       <c r="AT30" s="13" t="inlineStr">
@@ -11679,12 +11659,12 @@
       </c>
       <c r="AV30" s="14" t="inlineStr">
         <is>
-          <t>营口市 鲅鱼圈区 辽宁省 115007 CN</t>
+          <t>金华市 浙江省 322215 CN</t>
         </is>
       </c>
       <c r="AW30" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SPQY2QF85KOQ</t>
         </is>
       </c>
       <c r="AX30" s="13"/>
@@ -11693,51 +11673,51 @@
       <c r="BA30" s="13"/>
       <c r="BB30" s="13"/>
       <c r="BC30" s="13"/>
-      <c r="BD30" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD30" s="13"/>
       <c r="BE30" s="13"/>
       <c r="BF30" s="13"/>
       <c r="BG30" s="13"/>
       <c r="BH30" s="14"/>
       <c r="BI30" s="23"/>
-      <c r="BJ30" s="23"/>
-      <c r="BK30" s="23"/>
+      <c r="BJ30" s="23" t="inlineStr">
+        <is>
+          <t>855 g</t>
+        </is>
+      </c>
+      <c r="BK30" s="23" t="inlineStr">
+        <is>
+          <t>855.00 g</t>
+        </is>
+      </c>
       <c r="BL30" s="23" t="inlineStr">
         <is>
-          <t>32 x 29 x 21 cm</t>
-        </is>
-      </c>
-      <c r="BM30" s="23" t="inlineStr">
-        <is>
-          <t>32.00 x 29.00 x 21.00 cm</t>
-        </is>
-      </c>
+          <t>21L x 8l x 37H centimètres</t>
+        </is>
+      </c>
+      <c r="BM30" s="23"/>
       <c r="BN30" s="23" t="inlineStr">
         <is>
-          <t>2.2 kg</t>
+          <t>855 g</t>
         </is>
       </c>
       <c r="BO30" s="23" t="inlineStr">
         <is>
-          <t>2.20 kg</t>
+          <t>855.00 g</t>
         </is>
       </c>
       <c r="BP30" s="23" t="inlineStr">
         <is>
-          <t>32 x 29 x 21 cm</t>
+          <t>33 x 21 x 8 cm</t>
         </is>
       </c>
       <c r="BQ30" s="23" t="inlineStr">
         <is>
-          <t>32.00 x 29.00 x 21.00 cm</t>
+          <t>33.00 x 21.00 x 8.00 cm</t>
         </is>
       </c>
       <c r="BR30" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -11748,40 +11728,40 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0GWH1FGJB</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>Timisea</t>
+          <t>ALLILUYAA</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/Timisea/b/ref=bl_dp_s_web_93230377031?ie=UTF8&amp;node=93230377031&amp;field-lbr_brands_browse-bin=Timisea</t>
+          <t>https://www.amazon.fr/stores/ALLILUYAA/page/B6AAB331-17D2-444A-B3E5-494EC94DE846?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur anti-acariens 2 en 1 pour matelas, stérilisation à lumière bleue et haute fréquence, puissant nettoyeur de matelas</t>
+          <t>Aspirateur Matelas, Aspirateur Anti-Acariens, Vibration Haute Fréquence, Filtrage Trois Niveaux, Filtre Lavable, pour Canapés</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GWH1FGJB?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GYS43G8G?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0GWH1FGJB</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="M31" s="14" t="inlineStr">
@@ -11795,7 +11775,7 @@
         </is>
       </c>
       <c r="O31" s="15">
-        <v>335413</v>
+        <v>793789</v>
       </c>
       <c r="P31" s="15"/>
       <c r="Q31" s="16">
@@ -11808,7 +11788,7 @@
       </c>
       <c r="S31" s="18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T31" s="15"/>
@@ -11820,14 +11800,20 @@
         <v>1</v>
       </c>
       <c r="Z31" s="20">
-        <v>35.99</v>
+        <v>25.99</v>
       </c>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31" s="2"/>
-      <c r="AD31" s="19"/>
-      <c r="AE31" s="15"/>
-      <c r="AF31" s="21"/>
+      <c r="AD31" s="19">
+        <v>2</v>
+      </c>
+      <c r="AE31" s="15">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="21">
+        <v>1</v>
+      </c>
       <c r="AG31" s="22">
         <v>0</v>
       </c>
@@ -11835,37 +11821,39 @@
         <v>6.06</v>
       </c>
       <c r="AI31" s="16">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="AJ31"/>
       <c r="AK31" s="13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AL31" s="19">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="AM31" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN31" s="13"/>
       <c r="AO31" s="13"/>
       <c r="AP31"/>
-      <c r="AQ31" s="19"/>
+      <c r="AQ31" s="19">
+        <v>7</v>
+      </c>
       <c r="AR31" s="19">
         <v>1</v>
       </c>
       <c r="AS31" s="14" t="inlineStr">
         <is>
-          <t>Alloplectus</t>
+          <t>ALLILUYAA</t>
         </is>
       </c>
       <c r="AT31" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU31" s="13" t="inlineStr">
@@ -11875,12 +11863,12 @@
       </c>
       <c r="AV31" s="14" t="inlineStr">
         <is>
-          <t>金华市 浙江省 322215 CN</t>
+          <t>bayuquan LiaoNing 115007 CN</t>
         </is>
       </c>
       <c r="AW31" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SPQY2QF85KOQ</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A238ODZG8O3E58</t>
         </is>
       </c>
       <c r="AX31" s="13"/>
@@ -11897,38 +11885,42 @@
       <c r="BI31" s="23"/>
       <c r="BJ31" s="23" t="inlineStr">
         <is>
-          <t>855 g</t>
+          <t>430 g</t>
         </is>
       </c>
       <c r="BK31" s="23" t="inlineStr">
         <is>
-          <t>855.00 g</t>
+          <t>430.00 g</t>
         </is>
       </c>
       <c r="BL31" s="23" t="inlineStr">
         <is>
-          <t>21L x 8l x 37H centimètres</t>
-        </is>
-      </c>
-      <c r="BM31" s="23"/>
+          <t>1 x 1 x 1 cm</t>
+        </is>
+      </c>
+      <c r="BM31" s="23" t="inlineStr">
+        <is>
+          <t>1.00 x 1.00 x 1.00 cm</t>
+        </is>
+      </c>
       <c r="BN31" s="23" t="inlineStr">
         <is>
-          <t>855 g</t>
+          <t>430 g</t>
         </is>
       </c>
       <c r="BO31" s="23" t="inlineStr">
         <is>
-          <t>855.00 g</t>
+          <t>430.00 g</t>
         </is>
       </c>
       <c r="BP31" s="23" t="inlineStr">
         <is>
-          <t>33 x 21 x 8 cm</t>
+          <t>25.1 x 20.5 x 11.2 cm</t>
         </is>
       </c>
       <c r="BQ31" s="23" t="inlineStr">
         <is>
-          <t>33.00 x 21.00 x 8.00 cm</t>
+          <t>25.10 x 20.50 x 11.20 cm</t>
         </is>
       </c>
       <c r="BR31" s="13" t="inlineStr">
@@ -11944,40 +11936,40 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H1HSF3G6</t>
         </is>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>ALLILUYAA</t>
+          <t>Circlio</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/ALLILUYAA/page/B6AAB331-17D2-444A-B3E5-494EC94DE846?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/Circlio/page/4AF7FF6C-322D-46B8-9D85-131DE57A5144?lp_asin=B0H1HSF3G6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur Matelas, Aspirateur Anti-Acariens, Vibration Haute Fréquence, Filtrage Trois Niveaux, Filtre Lavable, pour Canapés</t>
+          <t>Circlio V20 Pro 18kPa Aspirateur Anti Acariens pour Matelas avec Lumière UVsDouble bac à Poussière | Punaise de Lit élimine</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GYS43G8G?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H1HSF3G6?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H1HSF3G6</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
@@ -11991,7 +11983,7 @@
         </is>
       </c>
       <c r="O32" s="15">
-        <v>793789</v>
+        <v>668431</v>
       </c>
       <c r="P32" s="15"/>
       <c r="Q32" s="16">
@@ -12004,7 +11996,7 @@
       </c>
       <c r="S32" s="18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="T32" s="15"/>
@@ -12016,37 +12008,37 @@
         <v>1</v>
       </c>
       <c r="Z32" s="20">
-        <v>25.99</v>
+        <v>119.99</v>
       </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE32" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF32" s="21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG32" s="22">
         <v>0</v>
       </c>
       <c r="AH32" s="20">
-        <v>6.06</v>
+        <v>8.03</v>
       </c>
       <c r="AI32" s="16">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AJ32"/>
       <c r="AK32" s="13" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AL32" s="19">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="AM32" s="13" t="inlineStr">
         <is>
@@ -12057,14 +12049,14 @@
       <c r="AO32" s="13"/>
       <c r="AP32"/>
       <c r="AQ32" s="19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR32" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS32" s="14" t="inlineStr">
         <is>
-          <t>ALLILUYAA</t>
+          <t>LUMIDRA</t>
         </is>
       </c>
       <c r="AT32" s="13" t="inlineStr">
@@ -12074,17 +12066,17 @@
       </c>
       <c r="AU32" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="AV32" s="14" t="inlineStr">
         <is>
-          <t>bayuquan LiaoNing 115007 CN</t>
+          <t>Romania 061331 RO</t>
         </is>
       </c>
       <c r="AW32" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A238ODZG8O3E58</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1MLES34OKJE35</t>
         </is>
       </c>
       <c r="AX32" s="13"/>
@@ -12092,7 +12084,11 @@
       <c r="AZ32" s="13"/>
       <c r="BA32" s="13"/>
       <c r="BB32" s="13"/>
-      <c r="BC32" s="13"/>
+      <c r="BC32" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD32" s="13"/>
       <c r="BE32" s="13"/>
       <c r="BF32" s="13"/>
@@ -12101,47 +12097,47 @@
       <c r="BI32" s="23"/>
       <c r="BJ32" s="23" t="inlineStr">
         <is>
-          <t>430 g</t>
+          <t>2 Kilograms</t>
         </is>
       </c>
       <c r="BK32" s="23" t="inlineStr">
         <is>
-          <t>430.00 g</t>
+          <t>2.00 kg</t>
         </is>
       </c>
       <c r="BL32" s="23" t="inlineStr">
         <is>
-          <t>1 x 1 x 1 cm</t>
+          <t>15 x 30 x 10 cm</t>
         </is>
       </c>
       <c r="BM32" s="23" t="inlineStr">
         <is>
-          <t>1.00 x 1.00 x 1.00 cm</t>
+          <t>15.00 x 30.00 x 10.00 cm</t>
         </is>
       </c>
       <c r="BN32" s="23" t="inlineStr">
         <is>
-          <t>430 g</t>
+          <t>2 kg</t>
         </is>
       </c>
       <c r="BO32" s="23" t="inlineStr">
         <is>
-          <t>430.00 g</t>
+          <t>2.00 kg</t>
         </is>
       </c>
       <c r="BP32" s="23" t="inlineStr">
         <is>
-          <t>25.1 x 20.5 x 11.2 cm</t>
+          <t>34.3 x 25.3 x 20.2 cm</t>
         </is>
       </c>
       <c r="BQ32" s="23" t="inlineStr">
         <is>
-          <t>25.10 x 20.50 x 11.20 cm</t>
+          <t>34.30 x 25.30 x 20.20 cm</t>
         </is>
       </c>
       <c r="BR32" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -12152,40 +12148,40 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0H1HSF3G6</t>
+          <t>B0H6F2NPXK</t>
         </is>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>Circlio</t>
+          <t>Lubluelu</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Circlio/page/4AF7FF6C-322D-46B8-9D85-131DE57A5144?lp_asin=B0H1HSF3G6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0H6F2NPXK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Circlio V20 Pro 18kPa Aspirateur Anti Acariens pour Matelas avec Lumière UVsDouble bac à Poussière | Punaise de Lit élimine</t>
+          <t>Lubluelu Nettoyeur de matelas 3 en 1 20 kPa, aspirateur anti-acariens avec fonction de frappe et fonction chauffante, aspirat</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H1HSF3G6?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H6F2NPXK?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41WpJwb0PhL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0H1HSF3G6</t>
+          <t>B0H6F2NPXK</t>
         </is>
       </c>
       <c r="M33" s="14" t="inlineStr">
@@ -12199,7 +12195,7 @@
         </is>
       </c>
       <c r="O33" s="15">
-        <v>668431</v>
+        <v>1569641</v>
       </c>
       <c r="P33" s="15"/>
       <c r="Q33" s="16">
@@ -12212,7 +12208,7 @@
       </c>
       <c r="S33" s="18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T33" s="15"/>
@@ -12224,37 +12220,35 @@
         <v>1</v>
       </c>
       <c r="Z33" s="20">
-        <v>119.99</v>
+        <v>79.99</v>
       </c>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="19">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AE33" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AF33" s="21">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AG33" s="22">
         <v>0</v>
       </c>
-      <c r="AH33" s="20">
-        <v>8.03</v>
-      </c>
+      <c r="AH33" s="20"/>
       <c r="AI33" s="16">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="AJ33"/>
       <c r="AK33" s="13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AL33" s="19">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AM33" s="13" t="inlineStr">
         <is>
@@ -12264,15 +12258,13 @@
       <c r="AN33" s="13"/>
       <c r="AO33" s="13"/>
       <c r="AP33"/>
-      <c r="AQ33" s="19">
-        <v>9</v>
-      </c>
+      <c r="AQ33" s="19"/>
       <c r="AR33" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS33" s="14" t="inlineStr">
         <is>
-          <t>LUMIDRA</t>
+          <t>Lubluelu Official</t>
         </is>
       </c>
       <c r="AT33" s="13" t="inlineStr">
@@ -12280,19 +12272,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU33" s="13" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="AV33" s="14" t="inlineStr">
-        <is>
-          <t>Romania 061331 RO</t>
-        </is>
-      </c>
+      <c r="AU33" s="13"/>
+      <c r="AV33" s="14"/>
       <c r="AW33" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1MLES34OKJE35</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N</t>
         </is>
       </c>
       <c r="AX33" s="13"/>
@@ -12300,11 +12284,7 @@
       <c r="AZ33" s="13"/>
       <c r="BA33" s="13"/>
       <c r="BB33" s="13"/>
-      <c r="BC33" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC33" s="13"/>
       <c r="BD33" s="13"/>
       <c r="BE33" s="13"/>
       <c r="BF33" s="13"/>
@@ -12313,49 +12293,25 @@
       <c r="BI33" s="23"/>
       <c r="BJ33" s="23" t="inlineStr">
         <is>
-          <t>2 Kilograms</t>
+          <t>1 Kilograms</t>
         </is>
       </c>
       <c r="BK33" s="23" t="inlineStr">
         <is>
-          <t>2.00 kg</t>
+          <t>1,000.00 g</t>
         </is>
       </c>
       <c r="BL33" s="23" t="inlineStr">
         <is>
-          <t>15 x 30 x 10 cm</t>
-        </is>
-      </c>
-      <c r="BM33" s="23" t="inlineStr">
-        <is>
-          <t>15.00 x 30.00 x 10.00 cm</t>
-        </is>
-      </c>
-      <c r="BN33" s="23" t="inlineStr">
-        <is>
-          <t>2 kg</t>
-        </is>
-      </c>
-      <c r="BO33" s="23" t="inlineStr">
-        <is>
-          <t>2.00 kg</t>
-        </is>
-      </c>
-      <c r="BP33" s="23" t="inlineStr">
-        <is>
-          <t>34.3 x 25.3 x 20.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ33" s="23" t="inlineStr">
-        <is>
-          <t>34.30 x 25.30 x 20.20 cm</t>
-        </is>
-      </c>
-      <c r="BR33" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+          <t>42L x 31l x 18H centimètres</t>
+        </is>
+      </c>
+      <c r="BM33" s="23"/>
+      <c r="BN33" s="23"/>
+      <c r="BO33" s="23"/>
+      <c r="BP33" s="23"/>
+      <c r="BQ33" s="23"/>
+      <c r="BR33" s="13"/>
     </row>
     <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
@@ -12364,40 +12320,40 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0H6F2NPXK</t>
+          <t>B0H8Z6R4ZK</t>
         </is>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu</t>
+          <t>Bcuuozeeing</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0H6F2NPXK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Nettoyeur de matelas 3 en 1 20 kPa, aspirateur anti-acariens avec fonction de frappe et fonction chauffante, aspirat</t>
+          <t>Aspirateur de matelas portable sans fil rechargeable pour lits, canapéssAspirateur à main silencieux, nettoyeur en profonde</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H6F2NPXK?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H8Z6R4ZK?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41WpJwb0PhL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41ei98pWxqL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0H6F2NPXK</t>
+          <t>B0H8Z6R4ZK</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -12405,28 +12361,12 @@
           <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
         </is>
       </c>
-      <c r="N34" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O34" s="15">
-        <v>1569641</v>
-      </c>
+      <c r="N34" s="14"/>
+      <c r="O34" s="15"/>
       <c r="P34" s="15"/>
-      <c r="Q34" s="16">
-        <v>0</v>
-      </c>
-      <c r="R34" s="17" t="inlineStr">
-        <is>
-          <t>Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="S34" s="18" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+      <c r="Q34" s="16"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="18"/>
       <c r="T34" s="15"/>
       <c r="U34" s="16"/>
       <c r="V34" s="15"/>
@@ -12436,20 +12376,16 @@
         <v>1</v>
       </c>
       <c r="Z34" s="20">
-        <v>79.99</v>
+        <v>16.9</v>
       </c>
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34" s="2"/>
-      <c r="AD34" s="19">
-        <v>16</v>
-      </c>
+      <c r="AD34" s="19"/>
       <c r="AE34" s="15">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="21">
-        <v>4.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF34" s="21"/>
       <c r="AG34" s="22">
         <v>0</v>
       </c>
@@ -12458,14 +12394,8 @@
         <v>0</v>
       </c>
       <c r="AJ34"/>
-      <c r="AK34" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="AL34" s="19">
-        <v>65</v>
-      </c>
+      <c r="AK34" s="13"/>
+      <c r="AL34" s="19"/>
       <c r="AM34" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -12480,7 +12410,7 @@
       </c>
       <c r="AS34" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Official</t>
+          <t>BozeRICH</t>
         </is>
       </c>
       <c r="AT34" s="13" t="inlineStr">
@@ -12492,7 +12422,7 @@
       <c r="AV34" s="14"/>
       <c r="AW34" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2H60F5LPAKHT8</t>
         </is>
       </c>
       <c r="AX34" s="13"/>
@@ -12509,17 +12439,17 @@
       <c r="BI34" s="23"/>
       <c r="BJ34" s="23" t="inlineStr">
         <is>
-          <t>1 Kilograms</t>
+          <t>550 g</t>
         </is>
       </c>
       <c r="BK34" s="23" t="inlineStr">
         <is>
-          <t>1,000.00 g</t>
+          <t>550.00 g</t>
         </is>
       </c>
       <c r="BL34" s="23" t="inlineStr">
         <is>
-          <t>42L x 31l x 18H centimètres</t>
+          <t>18L x 10l x 23H centimètres</t>
         </is>
       </c>
       <c r="BM34" s="23"/>
@@ -12528,152 +12458,6 @@
       <c r="BP34" s="23"/>
       <c r="BQ34" s="23"/>
       <c r="BR34" s="13"/>
-    </row>
-    <row r="35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13">
-        <v>34</v>
-      </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>B0H8Z6R4ZK</t>
-        </is>
-      </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>Bcuuozeeing</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>Aspirateur de matelas portable sans fil rechargeable pour lits, canapéssAspirateur à main silencieux, nettoyeur en profonde</t>
-        </is>
-      </c>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0H8Z6R4ZK?psc=1</t>
-        </is>
-      </c>
-      <c r="K35" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41ei98pWxqL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L35" s="14" t="inlineStr">
-        <is>
-          <t>B0H8Z6R4ZK</t>
-        </is>
-      </c>
-      <c r="M35" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="N35" s="14"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="18"/>
-      <c r="T35" s="15"/>
-      <c r="U35" s="16"/>
-      <c r="V35" s="15"/>
-      <c r="W35" s="15"/>
-      <c r="X35" s="15"/>
-      <c r="Y35" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z35" s="20">
-        <v>16.9</v>
-      </c>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35" s="2"/>
-      <c r="AD35" s="19"/>
-      <c r="AE35" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="21"/>
-      <c r="AG35" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="20"/>
-      <c r="AI35" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ35"/>
-      <c r="AK35" s="13"/>
-      <c r="AL35" s="19"/>
-      <c r="AM35" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN35" s="13"/>
-      <c r="AO35" s="13"/>
-      <c r="AP35"/>
-      <c r="AQ35" s="19"/>
-      <c r="AR35" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS35" s="14" t="inlineStr">
-        <is>
-          <t>BozeRICH</t>
-        </is>
-      </c>
-      <c r="AT35" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU35" s="13"/>
-      <c r="AV35" s="14"/>
-      <c r="AW35" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2H60F5LPAKHT8</t>
-        </is>
-      </c>
-      <c r="AX35" s="13"/>
-      <c r="AY35" s="13"/>
-      <c r="AZ35" s="13"/>
-      <c r="BA35" s="13"/>
-      <c r="BB35" s="13"/>
-      <c r="BC35" s="13"/>
-      <c r="BD35" s="13"/>
-      <c r="BE35" s="13"/>
-      <c r="BF35" s="13"/>
-      <c r="BG35" s="13"/>
-      <c r="BH35" s="14"/>
-      <c r="BI35" s="23"/>
-      <c r="BJ35" s="23" t="inlineStr">
-        <is>
-          <t>550 g</t>
-        </is>
-      </c>
-      <c r="BK35" s="23" t="inlineStr">
-        <is>
-          <t>550.00 g</t>
-        </is>
-      </c>
-      <c r="BL35" s="23" t="inlineStr">
-        <is>
-          <t>18L x 10l x 23H centimètres</t>
-        </is>
-      </c>
-      <c r="BM35" s="23"/>
-      <c r="BN35" s="23"/>
-      <c r="BO35" s="23"/>
-      <c r="BP35" s="23"/>
-      <c r="BQ35" s="23"/>
-      <c r="BR35" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12829,131 +12613,123 @@
     <hyperlink ref="M20" r:id="rId148" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N20" r:id="rId149"/>
     <hyperlink ref="AW20" r:id="rId150" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
-    <hyperlink ref="C21" r:id="rId151" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY"/>
-    <hyperlink ref="G21" r:id="rId152" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Hocomay"/>
-    <hyperlink ref="J21" r:id="rId153" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY?psc=1"/>
-    <hyperlink ref="K21" r:id="rId154" tooltip="https://m.media-amazon.com/images/I/41B77IYi3sL._AC_US600_.jpg"/>
-    <hyperlink ref="L21" r:id="rId155" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY"/>
+    <hyperlink ref="C21" r:id="rId151" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
+    <hyperlink ref="G21" r:id="rId152" tooltip="https://www.amazon.fr/stores/Tiazhan/page/E3AC215A-FE9C-439B-85FE-2B790F1088F2?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J21" r:id="rId153" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M?psc=1"/>
+    <hyperlink ref="K21" r:id="rId154" tooltip="https://images-na.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_US600_.jpg"/>
+    <hyperlink ref="L21" r:id="rId155" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
     <hyperlink ref="M21" r:id="rId156" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N21" r:id="rId157"/>
-    <hyperlink ref="AW21" r:id="rId158" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JWI8CSWZ8XWG"/>
-    <hyperlink ref="C22" r:id="rId159" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
-    <hyperlink ref="G22" r:id="rId160" tooltip="https://www.amazon.fr/stores/Tiazhan/page/E3AC215A-FE9C-439B-85FE-2B790F1088F2?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J22" r:id="rId161" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M?psc=1"/>
-    <hyperlink ref="K22" r:id="rId162" tooltip="https://images-na.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_US600_.jpg"/>
-    <hyperlink ref="L22" r:id="rId163" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
+    <hyperlink ref="AW21" r:id="rId158" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P6U062ILG5ZO"/>
+    <hyperlink ref="C22" r:id="rId159" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
+    <hyperlink ref="G22" r:id="rId160" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
+    <hyperlink ref="J22" r:id="rId161" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9?psc=1"/>
+    <hyperlink ref="K22" r:id="rId162" tooltip="https://images-na.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_US600_.jpg"/>
+    <hyperlink ref="L22" r:id="rId163" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
     <hyperlink ref="M22" r:id="rId164" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N22" r:id="rId165"/>
-    <hyperlink ref="AW22" r:id="rId166" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P6U062ILG5ZO"/>
-    <hyperlink ref="C23" r:id="rId167" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
-    <hyperlink ref="G23" r:id="rId168" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
-    <hyperlink ref="J23" r:id="rId169" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9?psc=1"/>
-    <hyperlink ref="K23" r:id="rId170" tooltip="https://images-na.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_US600_.jpg"/>
-    <hyperlink ref="L23" r:id="rId171" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
+    <hyperlink ref="AW22" r:id="rId166" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
+    <hyperlink ref="C23" r:id="rId167" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
+    <hyperlink ref="G23" r:id="rId168" tooltip="https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J23" r:id="rId169" tooltip="https://www.amazon.fr/dp/B0FDWVV95V?psc=1"/>
+    <hyperlink ref="K23" r:id="rId170" tooltip="https://images-na.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_US600_.jpg"/>
+    <hyperlink ref="L23" r:id="rId171" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
     <hyperlink ref="M23" r:id="rId172" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N23" r:id="rId173"/>
-    <hyperlink ref="AW23" r:id="rId174" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
-    <hyperlink ref="C24" r:id="rId175" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
-    <hyperlink ref="G24" r:id="rId176" tooltip="https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J24" r:id="rId177" tooltip="https://www.amazon.fr/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K24" r:id="rId178" tooltip="https://images-na.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_US600_.jpg"/>
-    <hyperlink ref="L24" r:id="rId179" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
+    <hyperlink ref="AW23" r:id="rId174" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1LBASE3VLPMEX"/>
+    <hyperlink ref="C24" r:id="rId175" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
+    <hyperlink ref="G24" r:id="rId176" tooltip="https://www.amazon.fr/Minthouz/b/ref=bl_dp_s_web_92236826031?ie=UTF8&amp;node=92236826031&amp;field-lbr_brands_browse-bin=Minthouz"/>
+    <hyperlink ref="J24" r:id="rId177" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1"/>
+    <hyperlink ref="K24" r:id="rId178" tooltip="https://images-na.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_US600_.jpg"/>
+    <hyperlink ref="L24" r:id="rId179" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
     <hyperlink ref="M24" r:id="rId180" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N24" r:id="rId181"/>
-    <hyperlink ref="AW24" r:id="rId182" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1LBASE3VLPMEX"/>
-    <hyperlink ref="C25" r:id="rId183" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
-    <hyperlink ref="G25" r:id="rId184" tooltip="https://www.amazon.fr/Minthouz/b/ref=bl_dp_s_web_92236826031?ie=UTF8&amp;node=92236826031&amp;field-lbr_brands_browse-bin=Minthouz"/>
-    <hyperlink ref="J25" r:id="rId185" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1"/>
-    <hyperlink ref="K25" r:id="rId186" tooltip="https://images-na.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_US600_.jpg"/>
-    <hyperlink ref="L25" r:id="rId187" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
+    <hyperlink ref="AW24" r:id="rId182" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A33KFCZH4G272M"/>
+    <hyperlink ref="C25" r:id="rId183" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
+    <hyperlink ref="G25" r:id="rId184" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J25" r:id="rId185" tooltip="https://www.amazon.fr/dp/B0FYM1D13D?psc=1"/>
+    <hyperlink ref="K25" r:id="rId186" tooltip="https://images-na.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_US600_.jpg"/>
+    <hyperlink ref="L25" r:id="rId187" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
     <hyperlink ref="M25" r:id="rId188" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N25" r:id="rId189"/>
-    <hyperlink ref="AW25" r:id="rId190" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A33KFCZH4G272M"/>
-    <hyperlink ref="C26" r:id="rId191" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
-    <hyperlink ref="G26" r:id="rId192" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J26" r:id="rId193" tooltip="https://www.amazon.fr/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K26" r:id="rId194" tooltip="https://images-na.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_US600_.jpg"/>
-    <hyperlink ref="L26" r:id="rId195" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
+    <hyperlink ref="AW25" r:id="rId190" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
+    <hyperlink ref="C26" r:id="rId191" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
+    <hyperlink ref="G26" r:id="rId192" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
+    <hyperlink ref="J26" r:id="rId193" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL?psc=1"/>
+    <hyperlink ref="K26" r:id="rId194" tooltip="https://images-na.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_US600_.jpg"/>
+    <hyperlink ref="L26" r:id="rId195" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
     <hyperlink ref="M26" r:id="rId196" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N26" r:id="rId197"/>
-    <hyperlink ref="AW26" r:id="rId198" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
-    <hyperlink ref="C27" r:id="rId199" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
-    <hyperlink ref="G27" r:id="rId200" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
-    <hyperlink ref="J27" r:id="rId201" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL?psc=1"/>
-    <hyperlink ref="K27" r:id="rId202" tooltip="https://images-na.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_US600_.jpg"/>
-    <hyperlink ref="L27" r:id="rId203" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
+    <hyperlink ref="AW26" r:id="rId198" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
+    <hyperlink ref="C27" r:id="rId199" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
+    <hyperlink ref="G27" r:id="rId200" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Ubric"/>
+    <hyperlink ref="J27" r:id="rId201" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1"/>
+    <hyperlink ref="K27" r:id="rId202" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/312AapwBZZL._AC_US600_.jpg"/>
+    <hyperlink ref="L27" r:id="rId203" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
     <hyperlink ref="M27" r:id="rId204" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N27" r:id="rId205"/>
-    <hyperlink ref="AW27" r:id="rId206" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
-    <hyperlink ref="C28" r:id="rId207" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
-    <hyperlink ref="G28" r:id="rId208" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Ubric"/>
-    <hyperlink ref="J28" r:id="rId209" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1"/>
-    <hyperlink ref="K28" r:id="rId210" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/312AapwBZZL._AC_US600_.jpg"/>
-    <hyperlink ref="L28" r:id="rId211" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
-    <hyperlink ref="M28" r:id="rId212" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="AW28" r:id="rId213" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2T66IN8FDYP42"/>
-    <hyperlink ref="C29" r:id="rId214" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
-    <hyperlink ref="G29" r:id="rId215" tooltip="https://www.amazon.fr/Elecbee/b/ref=bl_dp_s_web_52327091031?ie=UTF8&amp;node=52327091031&amp;field-lbr_brands_browse-bin=Elecbee"/>
-    <hyperlink ref="J29" r:id="rId216" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM?psc=1"/>
-    <hyperlink ref="K29" r:id="rId217" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/41tqM0+3BpL._AC_US600_.jpg"/>
-    <hyperlink ref="L29" r:id="rId218" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
-    <hyperlink ref="M29" r:id="rId219" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="AW29" r:id="rId220" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O"/>
-    <hyperlink ref="C30" r:id="rId221" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
-    <hyperlink ref="G30" r:id="rId222" tooltip="https://www.amazon.fr/XINYUDAILY/b/ref=bl_dp_s_web_85011884031?ie=UTF8&amp;node=85011884031&amp;field-lbr_brands_browse-bin=XINYUDAILY"/>
-    <hyperlink ref="J30" r:id="rId223" tooltip="https://www.amazon.fr/dp/B0GT17NK5X?psc=1"/>
-    <hyperlink ref="K30" r:id="rId224" tooltip="https://images-na.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_US600_.jpg"/>
-    <hyperlink ref="L30" r:id="rId225" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
+    <hyperlink ref="AW27" r:id="rId205" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2T66IN8FDYP42"/>
+    <hyperlink ref="C28" r:id="rId206" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
+    <hyperlink ref="G28" r:id="rId207" tooltip="https://www.amazon.fr/Elecbee/b/ref=bl_dp_s_web_52327091031?ie=UTF8&amp;node=52327091031&amp;field-lbr_brands_browse-bin=Elecbee"/>
+    <hyperlink ref="J28" r:id="rId208" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM?psc=1"/>
+    <hyperlink ref="K28" r:id="rId209" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/41tqM0+3BpL._AC_US600_.jpg"/>
+    <hyperlink ref="L28" r:id="rId210" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
+    <hyperlink ref="M28" r:id="rId211" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="AW28" r:id="rId212" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O"/>
+    <hyperlink ref="C29" r:id="rId213" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
+    <hyperlink ref="G29" r:id="rId214" tooltip="https://www.amazon.fr/XINYUDAILY/b/ref=bl_dp_s_web_85011884031?ie=UTF8&amp;node=85011884031&amp;field-lbr_brands_browse-bin=XINYUDAILY"/>
+    <hyperlink ref="J29" r:id="rId215" tooltip="https://www.amazon.fr/dp/B0GT17NK5X?psc=1"/>
+    <hyperlink ref="K29" r:id="rId216" tooltip="https://images-na.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId217" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
+    <hyperlink ref="M29" r:id="rId218" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N29" r:id="rId219"/>
+    <hyperlink ref="AW29" r:id="rId220" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY"/>
+    <hyperlink ref="C30" r:id="rId221" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
+    <hyperlink ref="G30" r:id="rId222" tooltip="https://www.amazon.fr/Timisea/b/ref=bl_dp_s_web_93230377031?ie=UTF8&amp;node=93230377031&amp;field-lbr_brands_browse-bin=Timisea"/>
+    <hyperlink ref="J30" r:id="rId223" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB?psc=1"/>
+    <hyperlink ref="K30" r:id="rId224" tooltip="https://images-na.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_US600_.jpg"/>
+    <hyperlink ref="L30" r:id="rId225" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
     <hyperlink ref="M30" r:id="rId226" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N30" r:id="rId227"/>
-    <hyperlink ref="AW30" r:id="rId228" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY"/>
-    <hyperlink ref="C31" r:id="rId229" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
-    <hyperlink ref="G31" r:id="rId230" tooltip="https://www.amazon.fr/Timisea/b/ref=bl_dp_s_web_93230377031?ie=UTF8&amp;node=93230377031&amp;field-lbr_brands_browse-bin=Timisea"/>
-    <hyperlink ref="J31" r:id="rId231" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB?psc=1"/>
-    <hyperlink ref="K31" r:id="rId232" tooltip="https://images-na.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId233" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
+    <hyperlink ref="AW30" r:id="rId228" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SPQY2QF85KOQ"/>
+    <hyperlink ref="C31" r:id="rId229" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
+    <hyperlink ref="G31" r:id="rId230" tooltip="https://www.amazon.fr/stores/ALLILUYAA/page/B6AAB331-17D2-444A-B3E5-494EC94DE846?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J31" r:id="rId231" tooltip="https://www.amazon.fr/dp/B0GYS43G8G?psc=1"/>
+    <hyperlink ref="K31" r:id="rId232" tooltip="https://images-na.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_US600_.jpg"/>
+    <hyperlink ref="L31" r:id="rId233" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
     <hyperlink ref="M31" r:id="rId234" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N31" r:id="rId235"/>
-    <hyperlink ref="AW31" r:id="rId236" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SPQY2QF85KOQ"/>
-    <hyperlink ref="C32" r:id="rId237" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
-    <hyperlink ref="G32" r:id="rId238" tooltip="https://www.amazon.fr/stores/ALLILUYAA/page/B6AAB331-17D2-444A-B3E5-494EC94DE846?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J32" r:id="rId239" tooltip="https://www.amazon.fr/dp/B0GYS43G8G?psc=1"/>
-    <hyperlink ref="K32" r:id="rId240" tooltip="https://images-na.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_US600_.jpg"/>
-    <hyperlink ref="L32" r:id="rId241" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
+    <hyperlink ref="AW31" r:id="rId236" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A238ODZG8O3E58"/>
+    <hyperlink ref="C32" r:id="rId237" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6"/>
+    <hyperlink ref="G32" r:id="rId238" tooltip="https://www.amazon.fr/stores/Circlio/page/4AF7FF6C-322D-46B8-9D85-131DE57A5144?lp_asin=B0H1HSF3G6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J32" r:id="rId239" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6?psc=1"/>
+    <hyperlink ref="K32" r:id="rId240" tooltip="https://images-na.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_US600_.jpg"/>
+    <hyperlink ref="L32" r:id="rId241" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6"/>
     <hyperlink ref="M32" r:id="rId242" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N32" r:id="rId243"/>
-    <hyperlink ref="AW32" r:id="rId244" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A238ODZG8O3E58"/>
-    <hyperlink ref="C33" r:id="rId245" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6"/>
-    <hyperlink ref="G33" r:id="rId246" tooltip="https://www.amazon.fr/stores/Circlio/page/4AF7FF6C-322D-46B8-9D85-131DE57A5144?lp_asin=B0H1HSF3G6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J33" r:id="rId247" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6?psc=1"/>
-    <hyperlink ref="K33" r:id="rId248" tooltip="https://images-na.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_US600_.jpg"/>
-    <hyperlink ref="L33" r:id="rId249" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6"/>
+    <hyperlink ref="AW32" r:id="rId244" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1MLES34OKJE35"/>
+    <hyperlink ref="C33" r:id="rId245" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
+    <hyperlink ref="G33" r:id="rId246" tooltip="https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0H6F2NPXK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J33" r:id="rId247" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK?psc=1"/>
+    <hyperlink ref="K33" r:id="rId248" tooltip="https://m.media-amazon.com/images/I/41WpJwb0PhL._AC_US600_.jpg"/>
+    <hyperlink ref="L33" r:id="rId249" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
     <hyperlink ref="M33" r:id="rId250" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N33" r:id="rId251"/>
-    <hyperlink ref="AW33" r:id="rId252" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1MLES34OKJE35"/>
-    <hyperlink ref="C34" r:id="rId253" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
-    <hyperlink ref="G34" r:id="rId254" tooltip="https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0H6F2NPXK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J34" r:id="rId255" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK?psc=1"/>
-    <hyperlink ref="K34" r:id="rId256" tooltip="https://m.media-amazon.com/images/I/41WpJwb0PhL._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId257" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
+    <hyperlink ref="AW33" r:id="rId252" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N"/>
+    <hyperlink ref="C34" r:id="rId253" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK"/>
+    <hyperlink ref="G34" r:id="rId254" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing"/>
+    <hyperlink ref="J34" r:id="rId255" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK?psc=1"/>
+    <hyperlink ref="K34" r:id="rId256" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41ei98pWxqL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId257" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK"/>
     <hyperlink ref="M34" r:id="rId258" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N34" r:id="rId259"/>
-    <hyperlink ref="AW34" r:id="rId260" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N"/>
-    <hyperlink ref="C35" r:id="rId261" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK"/>
-    <hyperlink ref="G35" r:id="rId262" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing"/>
-    <hyperlink ref="J35" r:id="rId263" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK?psc=1"/>
-    <hyperlink ref="K35" r:id="rId264" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41ei98pWxqL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId265" tooltip="https://www.amazon.fr/dp/B0H8Z6R4ZK"/>
-    <hyperlink ref="M35" r:id="rId266" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="AW35" r:id="rId267" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2H60F5LPAKHT8"/>
+    <hyperlink ref="AW34" r:id="rId259" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2H60F5LPAKHT8"/>
   </hyperlinks>
-  <drawing r:id="rId268"/>
+  <drawing r:id="rId260"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -13288,7 +13064,7 @@
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Hocomay</t>
+          <t>Liwankaqi</t>
         </is>
       </c>
       <c r="B16" s="15">
@@ -13307,7 +13083,7 @@
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi</t>
+          <t>Minthouz</t>
         </is>
       </c>
       <c r="B17" s="15">
@@ -13326,7 +13102,7 @@
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Minthouz</t>
+          <t>Nastopee</t>
         </is>
       </c>
       <c r="B18" s="15">
@@ -13345,7 +13121,7 @@
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Nastopee</t>
+          <t>SIKITUT</t>
         </is>
       </c>
       <c r="B19" s="15">
@@ -13364,7 +13140,7 @@
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>SIKITUT</t>
+          <t>Tiazhan</t>
         </is>
       </c>
       <c r="B20" s="15">
@@ -13383,7 +13159,7 @@
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Tiazhan</t>
+          <t>Timisea</t>
         </is>
       </c>
       <c r="B21" s="15">
@@ -13402,7 +13178,7 @@
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Timisea</t>
+          <t>Ubric</t>
         </is>
       </c>
       <c r="B22" s="15">
@@ -13421,7 +13197,7 @@
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>Ubric</t>
+          <t>Vihoom</t>
         </is>
       </c>
       <c r="B23" s="15">
@@ -13440,7 +13216,7 @@
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Vihoom</t>
+          <t>XINYUDAILY</t>
         </is>
       </c>
       <c r="B24" s="15">
@@ -13453,25 +13229,6 @@
       <c r="E24" s="15"/>
       <c r="F24" s="20"/>
       <c r="G24" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>XINYUDAILY</t>
-        </is>
-      </c>
-      <c r="B25" s="15">
-        <v>0</v>
-      </c>
-      <c r="C25" s="15">
-        <v>0</v>
-      </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="22">
         <v>0.0</v>
       </c>
     </row>
@@ -13483,7 +13240,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -13879,7 +13636,7 @@
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Luckily Baby</t>
+          <t>Minthouz EUDirect</t>
         </is>
       </c>
       <c r="B19" s="15">
@@ -13898,7 +13655,7 @@
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Minthouz EUDirect</t>
+          <t>NOEL AND RUTH JOHNSTON LTD</t>
         </is>
       </c>
       <c r="B20" s="15">
@@ -13917,7 +13674,7 @@
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>NOEL AND RUTH JOHNSTON LTD</t>
+          <t>PETERTOS Kft.</t>
         </is>
       </c>
       <c r="B21" s="15">
@@ -13936,7 +13693,7 @@
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>PETERTOS Kft.</t>
+          <t>SILVER LION Limited</t>
         </is>
       </c>
       <c r="B22" s="15">
@@ -13955,7 +13712,7 @@
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>SILVER LION Limited</t>
+          <t>Ubric</t>
         </is>
       </c>
       <c r="B23" s="15">
@@ -13974,7 +13731,7 @@
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Ubric</t>
+          <t>WUHAN RENHOTEC TECHNOLOGY LTD</t>
         </is>
       </c>
       <c r="B24" s="15">
@@ -13993,7 +13750,7 @@
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>WUHAN RENHOTEC TECHNOLOGY LTD</t>
+          <t>XINYU-EU</t>
         </is>
       </c>
       <c r="B25" s="15">
@@ -14012,7 +13769,7 @@
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>XINYU-EU</t>
+          <t>eusmarthousehold</t>
         </is>
       </c>
       <c r="B26" s="15">
@@ -14031,7 +13788,7 @@
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>eusmarthousehold</t>
+          <t>liwantech</t>
         </is>
       </c>
       <c r="B27" s="15">
@@ -14050,7 +13807,7 @@
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>liwantech</t>
+          <t>tengjidainzi</t>
         </is>
       </c>
       <c r="B28" s="15">
@@ -14063,25 +13820,6 @@
       <c r="E28" s="15"/>
       <c r="F28" s="20"/>
       <c r="G28" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>tengjidainzi</t>
-        </is>
-      </c>
-      <c r="B29" s="15">
-        <v>0</v>
-      </c>
-      <c r="C29" s="15">
-        <v>0</v>
-      </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="22">
         <v>0.0</v>
       </c>
     </row>
